--- a/Excel/JiaYuanPastureConfig.xlsx
+++ b/Excel/JiaYuanPastureConfig.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3514726C-5EFD-4C93-8EAA-1734CF260136}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7165BC3-1722-472B-B6B1-3835E50D87D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
     <author>作者</author>
   </authors>
   <commentList>
-    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{874F2130-3ADA-411C-A78F-71CE4E6A1D1E}">
+    <comment ref="H3" authorId="0" shapeId="0" xr:uid="{874F2130-3ADA-411C-A78F-71CE4E6A1D1E}">
       <text>
         <r>
           <rPr>
@@ -90,7 +90,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L3" authorId="0" shapeId="0" xr:uid="{2D59419F-9BC0-4EF7-ADBE-5C8FAEB50357}">
+    <comment ref="M3" authorId="0" shapeId="0" xr:uid="{2D59419F-9BC0-4EF7-ADBE-5C8FAEB50357}">
       <text>
         <r>
           <rPr>
@@ -121,7 +121,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="106">
   <si>
     <t>Id</t>
   </si>
@@ -396,6 +396,99 @@
   </si>
   <si>
     <t>27540,68850,165240,330480</t>
+  </si>
+  <si>
+    <t>Chicken</t>
+  </si>
+  <si>
+    <t>Duck</t>
+  </si>
+  <si>
+    <t>Rooster</t>
+  </si>
+  <si>
+    <t>Rabbit</t>
+  </si>
+  <si>
+    <t>Kitten</t>
+  </si>
+  <si>
+    <t>Dog</t>
+  </si>
+  <si>
+    <t>Pig</t>
+  </si>
+  <si>
+    <t>Cattle</t>
+  </si>
+  <si>
+    <t>Sheep</t>
+  </si>
+  <si>
+    <t>Donkey</t>
+  </si>
+  <si>
+    <t>Cow</t>
+  </si>
+  <si>
+    <t>Ostrich</t>
+  </si>
+  <si>
+    <t>Camel</t>
+  </si>
+  <si>
+    <t>Name_EN</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Goo-goo-goo...</t>
+  </si>
+  <si>
+    <t>Ga ga ga...</t>
+  </si>
+  <si>
+    <t>Cluck... Cluck...</t>
+  </si>
+  <si>
+    <t>Did you see my ears?</t>
+  </si>
+  <si>
+    <t>Where can I find something to eat?</t>
+  </si>
+  <si>
+    <t>Have you seen any bones anywhere?</t>
+  </si>
+  <si>
+    <t>Don't disturb me, I need to take a nap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moo... </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meow... </t>
+  </si>
+  <si>
+    <t>Every day is like this. I don't know if I'll be the one to eat next time.</t>
+  </si>
+  <si>
+    <t>The grass here is too small. I want to go outside and have a look.</t>
+  </si>
+  <si>
+    <t>The milk we produce is sold in many distant places!</t>
+  </si>
+  <si>
+    <t>Let's have a race!</t>
+  </si>
+  <si>
+    <t>I'm not thirsty. I can walk for a long time.</t>
+  </si>
+  <si>
+    <t>Speak_EN</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Des_EN</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2325,73 +2418,82 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C1:Q24"/>
+  <dimension ref="C1:T24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="6" width="17.875" customWidth="1"/>
-    <col min="7" max="7" width="25.75" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="14" width="16.75" customWidth="1"/>
-    <col min="15" max="15" width="16" customWidth="1"/>
-    <col min="16" max="17" width="14" customWidth="1"/>
+    <col min="4" max="7" width="17.875" customWidth="1"/>
+    <col min="8" max="8" width="25.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="16" width="16.75" customWidth="1"/>
+    <col min="17" max="18" width="16" customWidth="1"/>
+    <col min="19" max="20" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G1"/>
-      <c r="I1"/>
+    <row r="1" spans="3:20" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H1"/>
       <c r="J1"/>
-      <c r="M1"/>
+      <c r="K1"/>
+      <c r="N1"/>
     </row>
-    <row r="2" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="3" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="L3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="M3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="N3" s="7" t="s">
         <v>24</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="O3" s="3" t="s">
         <v>34</v>
       </c>
       <c r="P3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="S3" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="Q3" s="3" t="s">
+      <c r="T3" s="3" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C4" s="2" t="s">
         <v>0</v>
       </c>
@@ -2399,769 +2501,913 @@
         <v>4</v>
       </c>
       <c r="E4" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="F4" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="G4" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="H4" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="I4" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="L4" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="M4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="N4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="N4" s="3" t="s">
+      <c r="O4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="P4" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q4" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="P4" s="8" t="s">
+      <c r="R4" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="S4" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="Q4" s="8" t="s">
+      <c r="T4" s="8" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C5" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="G5" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="H5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="I5" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>1</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="K5" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="L5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="L5" s="3" t="s">
+      <c r="M5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="N5" s="3" t="s">
         <v>26</v>
-      </c>
-      <c r="N5" s="7" t="s">
-        <v>3</v>
       </c>
       <c r="O5" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="P5" s="3" t="s">
+      <c r="P5" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q5" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="R5" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="S5" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="Q5" s="3" t="s">
+      <c r="T5" s="3" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C6" s="5">
         <v>10001</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="F6" s="9">
         <v>1</v>
       </c>
-      <c r="F6" s="5">
+      <c r="G6" s="5">
         <v>10001</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="H6" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="H6" s="10">
+      <c r="I6" s="10">
         <v>1</v>
       </c>
-      <c r="I6" s="10">
+      <c r="J6" s="10">
         <v>900</v>
       </c>
-      <c r="J6" s="10">
-        <f>I6/2</f>
+      <c r="K6" s="10">
+        <f>J6/2</f>
         <v>450</v>
       </c>
-      <c r="K6" s="10">
+      <c r="L6" s="10">
         <v>2160.0000000000005</v>
       </c>
-      <c r="L6" s="10">
+      <c r="M6" s="10">
         <v>0.25</v>
       </c>
-      <c r="M6" s="12">
+      <c r="N6" s="12">
         <v>10035001</v>
-      </c>
-      <c r="N6" s="6" t="s">
-        <v>15</v>
       </c>
       <c r="O6" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="P6" s="10">
+      <c r="P6" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q6" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="R6" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="S6" s="10">
         <v>1</v>
       </c>
-      <c r="Q6" s="10">
+      <c r="T6" s="10">
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C7" s="5">
         <v>10002</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="F7" s="9">
         <v>2</v>
       </c>
-      <c r="F7" s="5">
+      <c r="G7" s="5">
         <v>10002</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="H7" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="H7" s="10">
+      <c r="I7" s="10">
         <v>1</v>
       </c>
-      <c r="I7" s="10">
+      <c r="J7" s="10">
         <v>1350</v>
       </c>
-      <c r="J7" s="10">
-        <f t="shared" ref="J7:J19" si="0">I7/2</f>
+      <c r="K7" s="10">
+        <f t="shared" ref="K7:K19" si="0">J7/2</f>
         <v>675</v>
       </c>
-      <c r="K7" s="10">
+      <c r="L7" s="10">
         <v>2700</v>
       </c>
-      <c r="L7" s="10">
+      <c r="M7" s="10">
         <v>0.25</v>
       </c>
-      <c r="M7" s="12">
+      <c r="N7" s="12">
         <v>10035002</v>
-      </c>
-      <c r="N7" s="6" t="s">
-        <v>16</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="P7" s="10">
+      <c r="P7" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q7" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="R7" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="S7" s="10">
         <v>2</v>
       </c>
-      <c r="Q7" s="10">
+      <c r="T7" s="10">
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C8" s="5">
         <v>10003</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="F8" s="9">
         <v>3</v>
       </c>
-      <c r="F8" s="5">
+      <c r="G8" s="5">
         <v>10003</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="H8" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="H8" s="10">
+      <c r="I8" s="10">
         <v>1</v>
       </c>
-      <c r="I8" s="10">
+      <c r="J8" s="10">
         <v>1800</v>
       </c>
-      <c r="J8" s="10">
+      <c r="K8" s="10">
         <f t="shared" si="0"/>
         <v>900</v>
       </c>
-      <c r="K8" s="10">
+      <c r="L8" s="10">
         <v>3239.9999999999991</v>
       </c>
-      <c r="L8" s="10">
+      <c r="M8" s="10">
         <v>0.25</v>
       </c>
-      <c r="M8" s="12">
+      <c r="N8" s="12">
         <v>10035003</v>
-      </c>
-      <c r="N8" s="6" t="s">
-        <v>17</v>
       </c>
       <c r="O8" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="P8" s="10">
+      <c r="P8" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="R8" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="S8" s="10">
         <v>3</v>
       </c>
-      <c r="Q8" s="10">
+      <c r="T8" s="10">
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C9" s="5">
         <v>10004</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="F9" s="9">
         <v>4</v>
       </c>
-      <c r="F9" s="5">
+      <c r="G9" s="5">
         <v>10004</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="H9" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="H9" s="10">
+      <c r="I9" s="10">
         <v>2</v>
       </c>
-      <c r="I9" s="10">
+      <c r="J9" s="10">
         <v>4500</v>
       </c>
-      <c r="J9" s="10">
+      <c r="K9" s="10">
         <f t="shared" si="0"/>
         <v>2250</v>
       </c>
-      <c r="K9" s="10">
+      <c r="L9" s="10">
         <v>3779.9999999999991</v>
       </c>
-      <c r="L9" s="10">
+      <c r="M9" s="10">
         <v>0.25</v>
       </c>
-      <c r="M9" s="12">
+      <c r="N9" s="12">
         <v>10035004</v>
-      </c>
-      <c r="N9" s="6" t="s">
-        <v>18</v>
       </c>
       <c r="O9" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="P9" s="10">
+      <c r="P9" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R9" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="S9" s="10">
         <v>5</v>
       </c>
-      <c r="Q9" s="10">
+      <c r="T9" s="10">
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C10" s="5">
         <v>10005</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="F10" s="9">
         <v>5</v>
       </c>
-      <c r="F10" s="5">
+      <c r="G10" s="5">
         <v>10005</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="H10" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="H10" s="10">
+      <c r="I10" s="10">
         <v>2</v>
       </c>
-      <c r="I10" s="10">
+      <c r="J10" s="10">
         <v>5400</v>
       </c>
-      <c r="J10" s="10">
+      <c r="K10" s="10">
         <f t="shared" si="0"/>
         <v>2700</v>
       </c>
-      <c r="K10" s="10">
+      <c r="L10" s="10">
         <v>4320.0000000000009</v>
       </c>
-      <c r="L10" s="10">
+      <c r="M10" s="10">
         <v>0.25</v>
       </c>
-      <c r="M10" s="12">
+      <c r="N10" s="12">
         <v>10035005</v>
-      </c>
-      <c r="N10" s="6" t="s">
-        <v>19</v>
       </c>
       <c r="O10" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="P10" s="10">
+      <c r="P10" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q10" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="R10" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="S10" s="10">
         <v>7</v>
       </c>
-      <c r="Q10" s="10">
+      <c r="T10" s="10">
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C11" s="5">
         <v>10006</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="F11" s="9">
         <v>6</v>
       </c>
-      <c r="F11" s="5">
+      <c r="G11" s="5">
         <v>10006</v>
       </c>
-      <c r="G11" s="11" t="s">
+      <c r="H11" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="H11" s="10">
+      <c r="I11" s="10">
         <v>2</v>
       </c>
-      <c r="I11" s="10">
+      <c r="J11" s="10">
         <v>6000</v>
       </c>
-      <c r="J11" s="10">
+      <c r="K11" s="10">
         <f t="shared" si="0"/>
         <v>3000</v>
       </c>
-      <c r="K11" s="10">
+      <c r="L11" s="10">
         <v>4860</v>
       </c>
-      <c r="L11" s="10">
+      <c r="M11" s="10">
         <v>0.25</v>
       </c>
-      <c r="M11" s="12">
+      <c r="N11" s="12">
         <v>10035006</v>
-      </c>
-      <c r="N11" s="6" t="s">
-        <v>62</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="P11" s="10">
+      <c r="P11" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q11" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="R11" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="S11" s="10">
         <v>9</v>
       </c>
-      <c r="Q11" s="10">
+      <c r="T11" s="10">
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C12" s="5">
         <v>10007</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="F12" s="9">
         <v>7</v>
       </c>
-      <c r="F12" s="5">
+      <c r="G12" s="5">
         <v>10007</v>
       </c>
-      <c r="G12" s="11" t="s">
+      <c r="H12" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="H12" s="10">
+      <c r="I12" s="10">
         <v>3</v>
       </c>
-      <c r="I12" s="10">
+      <c r="J12" s="10">
         <v>10350</v>
       </c>
-      <c r="J12" s="10">
+      <c r="K12" s="10">
         <f t="shared" si="0"/>
         <v>5175</v>
       </c>
-      <c r="K12" s="10">
+      <c r="L12" s="10">
         <v>5400</v>
       </c>
-      <c r="L12" s="10">
+      <c r="M12" s="10">
         <v>0.25</v>
       </c>
-      <c r="M12" s="12">
+      <c r="N12" s="12">
         <v>10035007</v>
-      </c>
-      <c r="N12" s="6" t="s">
-        <v>20</v>
       </c>
       <c r="O12" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="P12" s="10">
+      <c r="P12" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q12" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="R12" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="S12" s="10">
         <v>11</v>
       </c>
-      <c r="Q12" s="10">
+      <c r="T12" s="10">
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C13" s="5">
         <v>10008</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="F13" s="9">
         <v>8</v>
       </c>
-      <c r="F13" s="5">
+      <c r="G13" s="5">
         <v>10008</v>
       </c>
-      <c r="G13" s="11" t="s">
+      <c r="H13" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="H13" s="10">
+      <c r="I13" s="10">
         <v>3</v>
       </c>
-      <c r="I13" s="10">
+      <c r="J13" s="10">
         <v>11700</v>
       </c>
-      <c r="J13" s="10">
+      <c r="K13" s="10">
         <f t="shared" si="0"/>
         <v>5850</v>
       </c>
-      <c r="K13" s="10">
+      <c r="L13" s="10">
         <v>5940.0000000000009</v>
       </c>
-      <c r="L13" s="10">
+      <c r="M13" s="10">
         <v>0.25</v>
       </c>
-      <c r="M13" s="12">
+      <c r="N13" s="12">
         <v>10035008</v>
-      </c>
-      <c r="N13" s="6" t="s">
-        <v>21</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="P13" s="10">
+      <c r="P13" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q13" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="R13" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="S13" s="10">
         <v>13</v>
       </c>
-      <c r="Q13" s="10">
+      <c r="T13" s="10">
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C14" s="5">
         <v>10009</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="F14" s="9">
         <v>9</v>
       </c>
-      <c r="F14" s="5">
+      <c r="G14" s="5">
         <v>10009</v>
       </c>
-      <c r="G14" s="11" t="s">
+      <c r="H14" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="H14" s="10">
+      <c r="I14" s="10">
         <v>3</v>
       </c>
-      <c r="I14" s="10">
+      <c r="J14" s="10">
         <v>13500</v>
       </c>
-      <c r="J14" s="10">
+      <c r="K14" s="10">
         <f t="shared" si="0"/>
         <v>6750</v>
       </c>
-      <c r="K14" s="10">
+      <c r="L14" s="10">
         <v>5940.0000000000009</v>
       </c>
-      <c r="L14" s="10">
+      <c r="M14" s="10">
         <v>0.25</v>
       </c>
-      <c r="M14" s="12">
+      <c r="N14" s="12">
         <v>10035009</v>
-      </c>
-      <c r="N14" s="6" t="s">
-        <v>22</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="P14" s="10">
+      <c r="P14" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="R14" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="S14" s="10">
         <v>15</v>
       </c>
-      <c r="Q14" s="10">
+      <c r="T14" s="10">
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C15" s="5">
         <v>10010</v>
       </c>
       <c r="D15" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="F15" s="9">
         <v>10</v>
       </c>
-      <c r="F15" s="5">
+      <c r="G15" s="5">
         <v>10010</v>
       </c>
-      <c r="G15" s="11" t="s">
+      <c r="H15" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="H15" s="10">
+      <c r="I15" s="10">
         <v>3</v>
       </c>
-      <c r="I15" s="10">
+      <c r="J15" s="10">
         <v>15300</v>
       </c>
-      <c r="J15" s="10">
+      <c r="K15" s="10">
         <f t="shared" si="0"/>
         <v>7650</v>
       </c>
-      <c r="K15" s="10">
+      <c r="L15" s="10">
         <v>6479.9999999999982</v>
       </c>
-      <c r="L15" s="10">
+      <c r="M15" s="10">
         <v>0.25</v>
       </c>
-      <c r="M15" s="12">
+      <c r="N15" s="12">
         <v>10035010</v>
-      </c>
-      <c r="N15" s="6" t="s">
-        <v>63</v>
       </c>
       <c r="O15" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="P15" s="10">
+      <c r="P15" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q15" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="R15" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="S15" s="10">
         <v>17</v>
       </c>
-      <c r="Q15" s="10">
+      <c r="T15" s="10">
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C16" s="5">
         <v>10011</v>
       </c>
       <c r="D16" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="F16" s="9">
         <v>11</v>
       </c>
-      <c r="F16" s="5">
+      <c r="G16" s="5">
         <v>10011</v>
       </c>
-      <c r="G16" s="11" t="s">
+      <c r="H16" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="H16" s="10">
+      <c r="I16" s="10">
         <v>4</v>
       </c>
-      <c r="I16" s="10">
+      <c r="J16" s="10">
         <v>22800</v>
       </c>
-      <c r="J16" s="10">
+      <c r="K16" s="10">
         <f t="shared" si="0"/>
         <v>11400</v>
       </c>
-      <c r="K16" s="10">
+      <c r="L16" s="10">
         <v>6479.9999999999982</v>
       </c>
-      <c r="L16" s="10">
+      <c r="M16" s="10">
         <v>0.25</v>
       </c>
-      <c r="M16" s="12">
+      <c r="N16" s="12">
         <v>10035011</v>
-      </c>
-      <c r="N16" s="6" t="s">
-        <v>64</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="P16" s="10">
+      <c r="P16" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q16" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="R16" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="S16" s="10">
         <v>19</v>
       </c>
-      <c r="Q16" s="10">
+      <c r="T16" s="10">
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C17" s="5">
         <v>10012</v>
       </c>
       <c r="D17" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="F17" s="9">
         <v>12</v>
       </c>
-      <c r="F17" s="5">
+      <c r="G17" s="5">
         <v>10012</v>
       </c>
-      <c r="G17" s="11" t="s">
+      <c r="H17" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="H17" s="10">
+      <c r="I17" s="10">
         <v>4</v>
       </c>
-      <c r="I17" s="10">
+      <c r="J17" s="10">
         <v>25200</v>
       </c>
-      <c r="J17" s="10">
+      <c r="K17" s="10">
         <f t="shared" si="0"/>
         <v>12600</v>
       </c>
-      <c r="K17" s="10">
+      <c r="L17" s="10">
         <v>7020.0000000000018</v>
       </c>
-      <c r="L17" s="10">
+      <c r="M17" s="10">
         <v>0.25</v>
       </c>
-      <c r="M17" s="12">
+      <c r="N17" s="12">
         <v>10035012</v>
-      </c>
-      <c r="N17" s="6" t="s">
-        <v>55</v>
       </c>
       <c r="O17" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="P17" s="10">
+      <c r="P17" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q17" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="R17" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="S17" s="10">
         <v>21</v>
       </c>
-      <c r="Q17" s="10">
+      <c r="T17" s="10">
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C18" s="5">
         <v>10013</v>
       </c>
       <c r="D18" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E18" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="F18" s="9">
         <v>13</v>
       </c>
-      <c r="F18" s="5">
+      <c r="G18" s="5">
         <v>10013</v>
       </c>
-      <c r="G18" s="11" t="s">
+      <c r="H18" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="H18" s="10">
+      <c r="I18" s="10">
         <v>4</v>
       </c>
-      <c r="I18" s="10">
+      <c r="J18" s="10">
         <v>27600</v>
       </c>
-      <c r="J18" s="10">
+      <c r="K18" s="10">
         <f t="shared" si="0"/>
         <v>13800</v>
       </c>
-      <c r="K18" s="10">
+      <c r="L18" s="10">
         <v>7559.9999999999982</v>
       </c>
-      <c r="L18" s="10">
+      <c r="M18" s="10">
         <v>0.25</v>
       </c>
-      <c r="M18" s="12">
+      <c r="N18" s="12">
         <v>10035013</v>
-      </c>
-      <c r="N18" s="6" t="s">
-        <v>23</v>
       </c>
       <c r="O18" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="P18" s="10">
+      <c r="P18" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q18" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="Q18" s="10">
+      <c r="R18" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="S18" s="10">
+        <v>23</v>
+      </c>
+      <c r="T18" s="10">
         <v>100</v>
       </c>
     </row>
-    <row r="19" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C19" s="5">
         <v>10014</v>
       </c>
       <c r="D19" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="E19" s="9">
+      <c r="E19" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="F19" s="9">
         <v>14</v>
       </c>
-      <c r="F19" s="5">
+      <c r="G19" s="5">
         <v>10014</v>
       </c>
-      <c r="G19" s="11" t="s">
+      <c r="H19" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="H19" s="10">
+      <c r="I19" s="10">
         <v>4</v>
       </c>
-      <c r="I19" s="10">
+      <c r="J19" s="10">
         <v>30000</v>
       </c>
-      <c r="J19" s="10">
+      <c r="K19" s="10">
         <f t="shared" si="0"/>
         <v>15000</v>
       </c>
-      <c r="K19" s="10">
+      <c r="L19" s="10">
         <v>8100</v>
       </c>
-      <c r="L19" s="10">
+      <c r="M19" s="10">
         <v>0.25</v>
       </c>
-      <c r="M19" s="12">
+      <c r="N19" s="12">
         <v>10035014</v>
-      </c>
-      <c r="N19" s="6" t="s">
-        <v>56</v>
       </c>
       <c r="O19" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="P19" s="10">
+      <c r="P19" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q19" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="R19" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="S19" s="10">
         <v>25</v>
       </c>
-      <c r="Q19" s="10">
+      <c r="T19" s="10">
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="21" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="22" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="23" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="20" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="21" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="22" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" spans="3:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
